--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,2440 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122890359</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90962</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>544084</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6990233</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122890350</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>544315</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6990219</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122890354</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>544387</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6990122</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122890360</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90962</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>544063</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6990254</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122890342</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>544150</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6990154</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122890363</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90962</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>544363</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6990198</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122890357</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90962</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>544392</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6990123</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122890339</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>544528</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6990183</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122890348</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>544083</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6990302</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122890346</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>544020</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6990215</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122890356</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90962</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>544040</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6990284</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122890351</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>544331</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6990216</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122890345</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>544036</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6990229</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122890349</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>544303</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6990222</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122890344</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>544127</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6990227</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122890353</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>544396</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6990125</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122890338</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>544035</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6990216</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122890361</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90962</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>544037</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6990294</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122890355</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90962</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>544145</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6990101</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122890347</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>544037</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6990296</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bohål 3m upp</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122890358</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90962</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>544106</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6990214</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122890343</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>544140</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6990207</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122890352</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Flärkån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>544346</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6990141</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122890359</v>
+        <v>122890347</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +817,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544084</v>
+        <v>544037</v>
       </c>
       <c r="R3" t="n">
-        <v>6990233</v>
+        <v>6990296</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,6 +885,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bohål 3m upp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +916,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122890350</v>
+        <v>122890352</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -937,16 +950,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544315</v>
+        <v>544346</v>
       </c>
       <c r="R4" t="n">
-        <v>6990219</v>
+        <v>6990141</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,11 +1000,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122890354</v>
+        <v>122890338</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544387</v>
+        <v>544035</v>
       </c>
       <c r="R5" t="n">
-        <v>6990122</v>
+        <v>6990216</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,11 +1102,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122890360</v>
+        <v>122890353</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544063</v>
+        <v>544396</v>
       </c>
       <c r="R6" t="n">
-        <v>6990254</v>
+        <v>6990125</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,6 +1204,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122890342</v>
+        <v>122890343</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1259,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544150</v>
+        <v>544140</v>
       </c>
       <c r="R7" t="n">
-        <v>6990154</v>
+        <v>6990207</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1315,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122890363</v>
+        <v>122890348</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544363</v>
+        <v>544083</v>
       </c>
       <c r="R8" t="n">
-        <v>6990198</v>
+        <v>6990302</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,6 +1418,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122890357</v>
+        <v>122890355</v>
       </c>
       <c r="B9" t="n">
         <v>90962</v>
@@ -1468,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544392</v>
+        <v>544145</v>
       </c>
       <c r="R9" t="n">
-        <v>6990123</v>
+        <v>6990101</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1551,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122890339</v>
+        <v>122890346</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1564,24 +1585,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544528</v>
+        <v>544020</v>
       </c>
       <c r="R10" t="n">
-        <v>6990183</v>
+        <v>6990215</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,6 +1627,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122890348</v>
+        <v>122890357</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,21 +1674,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544083</v>
+        <v>544392</v>
       </c>
       <c r="R11" t="n">
-        <v>6990302</v>
+        <v>6990123</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,11 +1734,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1747,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122890346</v>
+        <v>122890354</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1787,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544020</v>
+        <v>544387</v>
       </c>
       <c r="R12" t="n">
-        <v>6990215</v>
+        <v>6990122</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122890356</v>
+        <v>122890345</v>
       </c>
       <c r="B13" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1870,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1894,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544040</v>
+        <v>544036</v>
       </c>
       <c r="R13" t="n">
-        <v>6990284</v>
+        <v>6990229</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,6 +1943,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122890351</v>
+        <v>122890360</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1972,38 +1990,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544331</v>
+        <v>544063</v>
       </c>
       <c r="R14" t="n">
-        <v>6990216</v>
+        <v>6990254</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,11 +2050,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2067,7 +2076,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122890345</v>
+        <v>122890344</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2107,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544036</v>
+        <v>544127</v>
       </c>
       <c r="R15" t="n">
-        <v>6990229</v>
+        <v>6990227</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,7 +2156,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2174,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122890349</v>
+        <v>122890361</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2190,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544303</v>
+        <v>544037</v>
       </c>
       <c r="R16" t="n">
-        <v>6990222</v>
+        <v>6990294</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,11 +2259,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2281,7 +2285,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122890344</v>
+        <v>122890339</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2315,16 +2319,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544127</v>
+        <v>544528</v>
       </c>
       <c r="R17" t="n">
-        <v>6990227</v>
+        <v>6990183</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,11 +2369,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2388,7 +2395,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122890353</v>
+        <v>122890342</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2428,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544396</v>
+        <v>544150</v>
       </c>
       <c r="R18" t="n">
-        <v>6990125</v>
+        <v>6990154</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2495,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122890338</v>
+        <v>122890351</v>
       </c>
       <c r="B19" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2511,31 +2518,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544035</v>
+        <v>544331</v>
       </c>
       <c r="R19" t="n">
         <v>6990216</v>
@@ -2571,6 +2582,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2597,10 +2613,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122890361</v>
+        <v>122890350</v>
       </c>
       <c r="B20" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2613,21 +2629,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2637,10 +2653,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544037</v>
+        <v>544315</v>
       </c>
       <c r="R20" t="n">
-        <v>6990294</v>
+        <v>6990219</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,6 +2689,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2699,7 +2720,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122890355</v>
+        <v>122890363</v>
       </c>
       <c r="B21" t="n">
         <v>90962</v>
@@ -2739,10 +2760,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544145</v>
+        <v>544363</v>
       </c>
       <c r="R21" t="n">
-        <v>6990101</v>
+        <v>6990198</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2801,10 +2822,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122890347</v>
+        <v>122890356</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,42 +2838,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544037</v>
+        <v>544040</v>
       </c>
       <c r="R22" t="n">
-        <v>6990296</v>
+        <v>6990284</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,11 +2898,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bohål 3m upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2916,7 +2924,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122890358</v>
+        <v>122890359</v>
       </c>
       <c r="B23" t="n">
         <v>90962</v>
@@ -2956,10 +2964,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544106</v>
+        <v>544084</v>
       </c>
       <c r="R23" t="n">
-        <v>6990214</v>
+        <v>6990233</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,7 +3026,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122890343</v>
+        <v>122890349</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3058,10 +3066,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544140</v>
+        <v>544303</v>
       </c>
       <c r="R24" t="n">
-        <v>6990207</v>
+        <v>6990222</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3098,7 +3106,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3125,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122890352</v>
+        <v>122890358</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3141,42 +3149,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544346</v>
+        <v>544106</v>
       </c>
       <c r="R25" t="n">
-        <v>6990141</v>
+        <v>6990214</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122890347</v>
+        <v>122890352</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544037</v>
+        <v>544346</v>
       </c>
       <c r="R3" t="n">
-        <v>6990296</v>
+        <v>6990141</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,11 +885,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bohål 3m upp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122890352</v>
+        <v>122890356</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,42 +927,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544346</v>
+        <v>544040</v>
       </c>
       <c r="R4" t="n">
-        <v>6990141</v>
+        <v>6990284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122890338</v>
+        <v>122890363</v>
       </c>
       <c r="B5" t="n">
-        <v>90944</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1029,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544035</v>
+        <v>544363</v>
       </c>
       <c r="R5" t="n">
-        <v>6990216</v>
+        <v>6990198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122890353</v>
+        <v>122890350</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1168,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544396</v>
+        <v>544315</v>
       </c>
       <c r="R6" t="n">
-        <v>6990125</v>
+        <v>6990219</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122890343</v>
+        <v>122890344</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1275,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544140</v>
+        <v>544127</v>
       </c>
       <c r="R7" t="n">
-        <v>6990207</v>
+        <v>6990227</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,7 +1329,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122890348</v>
+        <v>122890339</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1376,16 +1363,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544083</v>
+        <v>544528</v>
       </c>
       <c r="R8" t="n">
-        <v>6990302</v>
+        <v>6990183</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,11 +1413,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122890355</v>
+        <v>122890345</v>
       </c>
       <c r="B9" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544145</v>
+        <v>544036</v>
       </c>
       <c r="R9" t="n">
-        <v>6990101</v>
+        <v>6990229</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,6 +1515,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122890346</v>
+        <v>122890353</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1591,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544020</v>
+        <v>544396</v>
       </c>
       <c r="R10" t="n">
-        <v>6990215</v>
+        <v>6990125</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122890357</v>
+        <v>122890348</v>
       </c>
       <c r="B11" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544392</v>
+        <v>544083</v>
       </c>
       <c r="R11" t="n">
-        <v>6990123</v>
+        <v>6990302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,6 +1729,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122890354</v>
+        <v>122890346</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544387</v>
+        <v>544020</v>
       </c>
       <c r="R12" t="n">
-        <v>6990122</v>
+        <v>6990215</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,7 +1867,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122890345</v>
+        <v>122890343</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544036</v>
+        <v>544140</v>
       </c>
       <c r="R13" t="n">
-        <v>6990229</v>
+        <v>6990207</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122890360</v>
+        <v>122890338</v>
       </c>
       <c r="B14" t="n">
-        <v>90962</v>
+        <v>90944</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544063</v>
+        <v>544035</v>
       </c>
       <c r="R14" t="n">
-        <v>6990254</v>
+        <v>6990216</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2076,7 +2076,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122890344</v>
+        <v>122890351</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2110,16 +2110,20 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544127</v>
+        <v>544331</v>
       </c>
       <c r="R15" t="n">
-        <v>6990227</v>
+        <v>6990216</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122890361</v>
+        <v>122890355</v>
       </c>
       <c r="B16" t="n">
         <v>90962</v>
@@ -2223,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544037</v>
+        <v>544145</v>
       </c>
       <c r="R16" t="n">
-        <v>6990294</v>
+        <v>6990101</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122890339</v>
+        <v>122890359</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,42 +2305,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544528</v>
+        <v>544084</v>
       </c>
       <c r="R17" t="n">
-        <v>6990183</v>
+        <v>6990233</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122890342</v>
+        <v>122890357</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2435,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544150</v>
+        <v>544392</v>
       </c>
       <c r="R18" t="n">
-        <v>6990154</v>
+        <v>6990123</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,11 +2467,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,7 +2493,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122890351</v>
+        <v>122890354</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2536,20 +2527,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544331</v>
+        <v>544387</v>
       </c>
       <c r="R19" t="n">
-        <v>6990216</v>
+        <v>6990122</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,7 +2573,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2613,7 +2600,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122890350</v>
+        <v>122890349</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2653,10 +2640,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544315</v>
+        <v>544303</v>
       </c>
       <c r="R20" t="n">
-        <v>6990219</v>
+        <v>6990222</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,7 +2707,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122890363</v>
+        <v>122890361</v>
       </c>
       <c r="B21" t="n">
         <v>90962</v>
@@ -2760,10 +2747,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544363</v>
+        <v>544037</v>
       </c>
       <c r="R21" t="n">
-        <v>6990198</v>
+        <v>6990294</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2822,7 +2809,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122890356</v>
+        <v>122890358</v>
       </c>
       <c r="B22" t="n">
         <v>90962</v>
@@ -2862,10 +2849,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544040</v>
+        <v>544106</v>
       </c>
       <c r="R22" t="n">
-        <v>6990284</v>
+        <v>6990214</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2924,7 +2911,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122890359</v>
+        <v>122890360</v>
       </c>
       <c r="B23" t="n">
         <v>90962</v>
@@ -2964,10 +2951,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544084</v>
+        <v>544063</v>
       </c>
       <c r="R23" t="n">
-        <v>6990233</v>
+        <v>6990254</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3026,7 +3013,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122890349</v>
+        <v>122890342</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3066,10 +3053,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544303</v>
+        <v>544150</v>
       </c>
       <c r="R24" t="n">
-        <v>6990222</v>
+        <v>6990154</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3133,10 +3120,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122890358</v>
+        <v>122890347</v>
       </c>
       <c r="B25" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3149,34 +3136,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544106</v>
+        <v>544037</v>
       </c>
       <c r="R25" t="n">
-        <v>6990214</v>
+        <v>6990296</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3209,6 +3204,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bohål 3m upp</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -2600,10 +2600,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122890349</v>
+        <v>122890361</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2616,21 +2616,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544303</v>
+        <v>544037</v>
       </c>
       <c r="R20" t="n">
-        <v>6990222</v>
+        <v>6990294</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,11 +2676,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2707,10 +2702,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122890361</v>
+        <v>122890349</v>
       </c>
       <c r="B21" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2723,21 +2718,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2747,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544037</v>
+        <v>544303</v>
       </c>
       <c r="R21" t="n">
-        <v>6990294</v>
+        <v>6990222</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,6 +2778,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -2600,10 +2600,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122890361</v>
+        <v>122890349</v>
       </c>
       <c r="B20" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2616,21 +2616,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544037</v>
+        <v>544303</v>
       </c>
       <c r="R20" t="n">
-        <v>6990294</v>
+        <v>6990222</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,6 +2676,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2702,10 +2707,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122890349</v>
+        <v>122890361</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2718,21 +2723,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2742,10 +2747,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544303</v>
+        <v>544037</v>
       </c>
       <c r="R21" t="n">
-        <v>6990222</v>
+        <v>6990294</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,11 +2783,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122890352</v>
+        <v>122890363</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,42 +817,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544346</v>
+        <v>544363</v>
       </c>
       <c r="R3" t="n">
-        <v>6990141</v>
+        <v>6990198</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -911,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122890356</v>
+        <v>122890359</v>
       </c>
       <c r="B4" t="n">
         <v>90962</v>
@@ -951,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544040</v>
+        <v>544084</v>
       </c>
       <c r="R4" t="n">
-        <v>6990284</v>
+        <v>6990233</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122890363</v>
+        <v>122890349</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544363</v>
+        <v>544303</v>
       </c>
       <c r="R5" t="n">
-        <v>6990198</v>
+        <v>6990222</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,6 +1081,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122890350</v>
+        <v>122890354</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1155,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544315</v>
+        <v>544387</v>
       </c>
       <c r="R6" t="n">
-        <v>6990219</v>
+        <v>6990122</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122890344</v>
+        <v>122890360</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,21 +1235,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1262,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544127</v>
+        <v>544063</v>
       </c>
       <c r="R7" t="n">
-        <v>6990227</v>
+        <v>6990254</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,11 +1295,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122890339</v>
+        <v>122890358</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,42 +1337,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544528</v>
+        <v>544106</v>
       </c>
       <c r="R8" t="n">
-        <v>6990183</v>
+        <v>6990214</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122890345</v>
+        <v>122890361</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1455,21 +1439,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544036</v>
+        <v>544037</v>
       </c>
       <c r="R9" t="n">
-        <v>6990229</v>
+        <v>6990294</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,11 +1499,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,7 +1525,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122890353</v>
+        <v>122890350</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1586,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544396</v>
+        <v>544315</v>
       </c>
       <c r="R10" t="n">
-        <v>6990125</v>
+        <v>6990219</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,7 +1632,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122890348</v>
+        <v>122890351</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1687,16 +1666,20 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544083</v>
+        <v>544331</v>
       </c>
       <c r="R11" t="n">
-        <v>6990302</v>
+        <v>6990216</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,7 +1743,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122890346</v>
+        <v>122890342</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1800,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544020</v>
+        <v>544150</v>
       </c>
       <c r="R12" t="n">
-        <v>6990215</v>
+        <v>6990154</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,7 +1850,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122890343</v>
+        <v>122890344</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1907,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544140</v>
+        <v>544127</v>
       </c>
       <c r="R13" t="n">
-        <v>6990207</v>
+        <v>6990227</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122890338</v>
+        <v>122890339</v>
       </c>
       <c r="B14" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,34 +1973,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544035</v>
+        <v>544528</v>
       </c>
       <c r="R14" t="n">
-        <v>6990216</v>
+        <v>6990183</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2076,7 +2067,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122890351</v>
+        <v>122890346</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2110,20 +2101,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544331</v>
+        <v>544020</v>
       </c>
       <c r="R15" t="n">
-        <v>6990216</v>
+        <v>6990215</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,7 +2147,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122890355</v>
+        <v>122890352</v>
       </c>
       <c r="B16" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,34 +2190,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544145</v>
+        <v>544346</v>
       </c>
       <c r="R16" t="n">
-        <v>6990101</v>
+        <v>6990141</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,7 +2284,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122890359</v>
+        <v>122890357</v>
       </c>
       <c r="B17" t="n">
         <v>90962</v>
@@ -2329,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544084</v>
+        <v>544392</v>
       </c>
       <c r="R17" t="n">
-        <v>6990233</v>
+        <v>6990123</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122890357</v>
+        <v>122890345</v>
       </c>
       <c r="B18" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,21 +2402,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544392</v>
+        <v>544036</v>
       </c>
       <c r="R18" t="n">
-        <v>6990123</v>
+        <v>6990229</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,6 +2462,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2493,7 +2493,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122890354</v>
+        <v>122890347</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2527,16 +2527,24 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544387</v>
+        <v>544037</v>
       </c>
       <c r="R19" t="n">
-        <v>6990122</v>
+        <v>6990296</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2581,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål 3m upp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2600,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122890349</v>
+        <v>122890338</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2616,21 +2624,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2640,10 +2648,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544303</v>
+        <v>544035</v>
       </c>
       <c r="R20" t="n">
-        <v>6990222</v>
+        <v>6990216</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,11 +2684,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2707,7 +2710,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122890361</v>
+        <v>122890355</v>
       </c>
       <c r="B21" t="n">
         <v>90962</v>
@@ -2747,10 +2750,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544037</v>
+        <v>544145</v>
       </c>
       <c r="R21" t="n">
-        <v>6990294</v>
+        <v>6990101</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2809,10 +2812,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122890358</v>
+        <v>122890348</v>
       </c>
       <c r="B22" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2825,21 +2828,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2849,10 +2852,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544106</v>
+        <v>544083</v>
       </c>
       <c r="R22" t="n">
-        <v>6990214</v>
+        <v>6990302</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,6 +2888,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2911,10 +2919,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122890360</v>
+        <v>122890353</v>
       </c>
       <c r="B23" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2927,21 +2935,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2951,10 +2959,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544063</v>
+        <v>544396</v>
       </c>
       <c r="R23" t="n">
-        <v>6990254</v>
+        <v>6990125</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,6 +2995,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3013,7 +3026,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122890342</v>
+        <v>122890343</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3053,10 +3066,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544150</v>
+        <v>544140</v>
       </c>
       <c r="R24" t="n">
-        <v>6990154</v>
+        <v>6990207</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,7 +3106,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3120,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122890347</v>
+        <v>122890356</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3136,42 +3149,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544037</v>
+        <v>544040</v>
       </c>
       <c r="R25" t="n">
-        <v>6990296</v>
+        <v>6990284</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,11 +3209,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Bohål 3m upp</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122890363</v>
+        <v>122890351</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +817,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544363</v>
+        <v>544331</v>
       </c>
       <c r="R3" t="n">
-        <v>6990198</v>
+        <v>6990216</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,6 +881,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122890359</v>
+        <v>122890347</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +928,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544084</v>
+        <v>544037</v>
       </c>
       <c r="R4" t="n">
-        <v>6990233</v>
+        <v>6990296</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,6 +996,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bohål 3m upp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1112,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122890354</v>
+        <v>122890355</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544387</v>
+        <v>544145</v>
       </c>
       <c r="R6" t="n">
-        <v>6990122</v>
+        <v>6990101</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,11 +1210,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122890360</v>
+        <v>122890343</v>
       </c>
       <c r="B7" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,21 +1252,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544063</v>
+        <v>544140</v>
       </c>
       <c r="R7" t="n">
-        <v>6990254</v>
+        <v>6990207</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,6 +1312,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122890358</v>
+        <v>122890361</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544106</v>
+        <v>544037</v>
       </c>
       <c r="R8" t="n">
-        <v>6990214</v>
+        <v>6990294</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122890361</v>
+        <v>122890338</v>
       </c>
       <c r="B9" t="n">
-        <v>90962</v>
+        <v>90952</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,21 +1461,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1463,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544037</v>
+        <v>544035</v>
       </c>
       <c r="R9" t="n">
-        <v>6990294</v>
+        <v>6990216</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1547,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122890350</v>
+        <v>122890352</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1559,16 +1581,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544315</v>
+        <v>544346</v>
       </c>
       <c r="R10" t="n">
-        <v>6990219</v>
+        <v>6990141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,11 +1631,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,7 +1657,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122890351</v>
+        <v>122890354</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1666,20 +1691,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544331</v>
+        <v>544387</v>
       </c>
       <c r="R11" t="n">
-        <v>6990216</v>
+        <v>6990122</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,7 +1737,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122890342</v>
+        <v>122890359</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,21 +1780,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544150</v>
+        <v>544084</v>
       </c>
       <c r="R12" t="n">
-        <v>6990154</v>
+        <v>6990233</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,11 +1840,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,7 +1866,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122890344</v>
+        <v>122890345</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1890,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544127</v>
+        <v>544036</v>
       </c>
       <c r="R13" t="n">
-        <v>6990227</v>
+        <v>6990229</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1946,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,7 +1973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122890339</v>
+        <v>122890342</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -1991,24 +2007,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544528</v>
+        <v>544150</v>
       </c>
       <c r="R14" t="n">
-        <v>6990183</v>
+        <v>6990154</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,6 +2049,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2067,7 +2080,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122890346</v>
+        <v>122890350</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2107,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544020</v>
+        <v>544315</v>
       </c>
       <c r="R15" t="n">
-        <v>6990215</v>
+        <v>6990219</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122890352</v>
+        <v>122890344</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2208,24 +2221,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544346</v>
+        <v>544127</v>
       </c>
       <c r="R16" t="n">
-        <v>6990141</v>
+        <v>6990227</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,6 +2263,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2284,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122890357</v>
+        <v>122890356</v>
       </c>
       <c r="B17" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2324,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544392</v>
+        <v>544040</v>
       </c>
       <c r="R17" t="n">
-        <v>6990123</v>
+        <v>6990284</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122890345</v>
+        <v>122890358</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2402,21 +2412,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2426,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544036</v>
+        <v>544106</v>
       </c>
       <c r="R18" t="n">
-        <v>6990229</v>
+        <v>6990214</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,11 +2472,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2493,7 +2498,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122890347</v>
+        <v>122890346</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2527,24 +2532,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544037</v>
+        <v>544020</v>
       </c>
       <c r="R19" t="n">
-        <v>6990296</v>
+        <v>6990215</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,7 +2578,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Bohål 3m upp</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,10 +2605,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122890338</v>
+        <v>122890348</v>
       </c>
       <c r="B20" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2624,21 +2621,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2648,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544035</v>
+        <v>544083</v>
       </c>
       <c r="R20" t="n">
-        <v>6990216</v>
+        <v>6990302</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2684,6 +2681,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2710,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122890355</v>
+        <v>122890363</v>
       </c>
       <c r="B21" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2750,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544145</v>
+        <v>544363</v>
       </c>
       <c r="R21" t="n">
-        <v>6990101</v>
+        <v>6990198</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2812,10 +2814,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122890348</v>
+        <v>122890357</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2828,21 +2830,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2852,10 +2854,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544083</v>
+        <v>544392</v>
       </c>
       <c r="R22" t="n">
-        <v>6990302</v>
+        <v>6990123</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2888,11 +2890,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3026,7 +3023,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122890343</v>
+        <v>122890339</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3060,16 +3057,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544140</v>
+        <v>544528</v>
       </c>
       <c r="R24" t="n">
-        <v>6990207</v>
+        <v>6990183</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3102,11 +3107,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3133,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122890356</v>
+        <v>122890360</v>
       </c>
       <c r="B25" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544040</v>
+        <v>544063</v>
       </c>
       <c r="R25" t="n">
-        <v>6990284</v>
+        <v>6990254</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -2605,10 +2605,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122890348</v>
+        <v>122890363</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544083</v>
+        <v>544363</v>
       </c>
       <c r="R20" t="n">
-        <v>6990302</v>
+        <v>6990198</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,11 +2681,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,10 +2707,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122890363</v>
+        <v>122890348</v>
       </c>
       <c r="B21" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2728,21 +2723,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2752,10 +2747,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544363</v>
+        <v>544083</v>
       </c>
       <c r="R21" t="n">
-        <v>6990198</v>
+        <v>6990302</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,6 +2783,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122890351</v>
+        <v>122890353</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -835,20 +835,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544331</v>
+        <v>544396</v>
       </c>
       <c r="R3" t="n">
-        <v>6990216</v>
+        <v>6990125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +881,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122890347</v>
+        <v>122890346</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -946,24 +942,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544037</v>
+        <v>544020</v>
       </c>
       <c r="R4" t="n">
-        <v>6990296</v>
+        <v>6990215</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bohål 3m upp</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122890349</v>
+        <v>122890351</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1061,16 +1049,20 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544303</v>
+        <v>544331</v>
       </c>
       <c r="R5" t="n">
-        <v>6990222</v>
+        <v>6990216</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,7 +1099,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122890355</v>
+        <v>122890338</v>
       </c>
       <c r="B6" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544145</v>
+        <v>544035</v>
       </c>
       <c r="R6" t="n">
-        <v>6990101</v>
+        <v>6990216</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1228,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122890343</v>
+        <v>122890354</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1276,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544140</v>
+        <v>544387</v>
       </c>
       <c r="R7" t="n">
-        <v>6990207</v>
+        <v>6990122</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,7 +1308,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1445,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122890338</v>
+        <v>122890349</v>
       </c>
       <c r="B9" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544035</v>
+        <v>544303</v>
       </c>
       <c r="R9" t="n">
-        <v>6990216</v>
+        <v>6990222</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,6 +1513,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122890352</v>
+        <v>122890360</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,42 +1560,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544346</v>
+        <v>544063</v>
       </c>
       <c r="R10" t="n">
-        <v>6990141</v>
+        <v>6990254</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122890354</v>
+        <v>122890358</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,21 +1662,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1697,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544387</v>
+        <v>544106</v>
       </c>
       <c r="R11" t="n">
-        <v>6990122</v>
+        <v>6990214</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,11 +1722,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122890359</v>
+        <v>122890343</v>
       </c>
       <c r="B12" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,21 +1764,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544084</v>
+        <v>544140</v>
       </c>
       <c r="R12" t="n">
-        <v>6990233</v>
+        <v>6990207</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,6 +1824,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,7 +1855,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122890345</v>
+        <v>122890348</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1906,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544036</v>
+        <v>544083</v>
       </c>
       <c r="R13" t="n">
-        <v>6990229</v>
+        <v>6990302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1935,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122890342</v>
+        <v>122890356</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,21 +1978,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2013,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544150</v>
+        <v>544040</v>
       </c>
       <c r="R14" t="n">
-        <v>6990154</v>
+        <v>6990284</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,11 +2038,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122890350</v>
+        <v>122890363</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,21 +2080,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2120,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544315</v>
+        <v>544363</v>
       </c>
       <c r="R15" t="n">
-        <v>6990219</v>
+        <v>6990198</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,11 +2140,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122890344</v>
+        <v>122890355</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,21 +2182,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2227,10 +2206,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544127</v>
+        <v>544145</v>
       </c>
       <c r="R16" t="n">
-        <v>6990227</v>
+        <v>6990101</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,11 +2242,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,7 +2268,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122890356</v>
+        <v>122890359</v>
       </c>
       <c r="B17" t="n">
         <v>90970</v>
@@ -2334,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544040</v>
+        <v>544084</v>
       </c>
       <c r="R17" t="n">
-        <v>6990284</v>
+        <v>6990233</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2396,10 +2370,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122890358</v>
+        <v>122890350</v>
       </c>
       <c r="B18" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,21 +2386,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544106</v>
+        <v>544315</v>
       </c>
       <c r="R18" t="n">
-        <v>6990214</v>
+        <v>6990219</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,6 +2446,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2498,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122890346</v>
+        <v>122890357</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2538,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544020</v>
+        <v>544392</v>
       </c>
       <c r="R19" t="n">
-        <v>6990215</v>
+        <v>6990123</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,11 +2553,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,10 +2579,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122890363</v>
+        <v>122890344</v>
       </c>
       <c r="B20" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,21 +2595,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2619,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544363</v>
+        <v>544127</v>
       </c>
       <c r="R20" t="n">
-        <v>6990198</v>
+        <v>6990227</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,6 +2655,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2707,7 +2686,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122890348</v>
+        <v>122890339</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2741,16 +2720,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544083</v>
+        <v>544528</v>
       </c>
       <c r="R21" t="n">
-        <v>6990302</v>
+        <v>6990183</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,11 +2770,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2814,10 +2796,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122890357</v>
+        <v>122890345</v>
       </c>
       <c r="B22" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2830,21 +2812,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2854,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544392</v>
+        <v>544036</v>
       </c>
       <c r="R22" t="n">
-        <v>6990123</v>
+        <v>6990229</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,6 +2872,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2916,7 +2903,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122890353</v>
+        <v>122890347</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2950,16 +2937,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544396</v>
+        <v>544037</v>
       </c>
       <c r="R23" t="n">
-        <v>6990125</v>
+        <v>6990296</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,7 +2991,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål 3m upp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3023,7 +3018,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122890339</v>
+        <v>122890342</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3057,24 +3052,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544528</v>
+        <v>544150</v>
       </c>
       <c r="R24" t="n">
-        <v>6990183</v>
+        <v>6990154</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3107,6 +3094,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3133,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122890360</v>
+        <v>122890352</v>
       </c>
       <c r="B25" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3149,34 +3141,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544063</v>
+        <v>544346</v>
       </c>
       <c r="R25" t="n">
-        <v>6990254</v>
+        <v>6990141</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122890361</v>
+        <v>122890349</v>
       </c>
       <c r="B8" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544037</v>
+        <v>544303</v>
       </c>
       <c r="R8" t="n">
-        <v>6990294</v>
+        <v>6990222</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,6 +1411,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122890349</v>
+        <v>122890361</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544303</v>
+        <v>544037</v>
       </c>
       <c r="R9" t="n">
-        <v>6990222</v>
+        <v>6990294</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,11 +1518,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1855,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122890348</v>
+        <v>122890356</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544083</v>
+        <v>544040</v>
       </c>
       <c r="R13" t="n">
-        <v>6990302</v>
+        <v>6990284</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,11 +1931,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122890356</v>
+        <v>122890348</v>
       </c>
       <c r="B14" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544040</v>
+        <v>544083</v>
       </c>
       <c r="R14" t="n">
-        <v>6990284</v>
+        <v>6990302</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,6 +2033,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122890353</v>
+        <v>122890342</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544396</v>
+        <v>544150</v>
       </c>
       <c r="R3" t="n">
-        <v>6990125</v>
+        <v>6990154</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122890346</v>
+        <v>122890358</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544020</v>
+        <v>544106</v>
       </c>
       <c r="R4" t="n">
-        <v>6990215</v>
+        <v>6990214</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,11 +984,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122890351</v>
+        <v>122890352</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1051,7 +1046,11 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544331</v>
+        <v>544346</v>
       </c>
       <c r="R5" t="n">
-        <v>6990216</v>
+        <v>6990141</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,11 +1094,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122890338</v>
+        <v>122890359</v>
       </c>
       <c r="B6" t="n">
-        <v>90952</v>
+        <v>90970</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544035</v>
+        <v>544084</v>
       </c>
       <c r="R6" t="n">
-        <v>6990216</v>
+        <v>6990233</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122890354</v>
+        <v>122890351</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1262,16 +1256,20 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544387</v>
+        <v>544331</v>
       </c>
       <c r="R7" t="n">
-        <v>6990122</v>
+        <v>6990216</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1306,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,7 +1333,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122890349</v>
+        <v>122890345</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1375,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544303</v>
+        <v>544036</v>
       </c>
       <c r="R8" t="n">
-        <v>6990222</v>
+        <v>6990229</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122890361</v>
+        <v>122890343</v>
       </c>
       <c r="B9" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1456,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544037</v>
+        <v>544140</v>
       </c>
       <c r="R9" t="n">
-        <v>6990294</v>
+        <v>6990207</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,6 +1516,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,7 +1547,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122890360</v>
+        <v>122890355</v>
       </c>
       <c r="B10" t="n">
         <v>90970</v>
@@ -1584,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544063</v>
+        <v>544145</v>
       </c>
       <c r="R10" t="n">
-        <v>6990254</v>
+        <v>6990101</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122890358</v>
+        <v>122890348</v>
       </c>
       <c r="B11" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,21 +1665,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1686,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544106</v>
+        <v>544083</v>
       </c>
       <c r="R11" t="n">
-        <v>6990214</v>
+        <v>6990302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,6 +1725,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,7 +1756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122890343</v>
+        <v>122890354</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1788,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544140</v>
+        <v>544387</v>
       </c>
       <c r="R12" t="n">
-        <v>6990207</v>
+        <v>6990122</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1828,7 +1836,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,7 +1863,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122890356</v>
+        <v>122890360</v>
       </c>
       <c r="B13" t="n">
         <v>90970</v>
@@ -1895,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544040</v>
+        <v>544063</v>
       </c>
       <c r="R13" t="n">
-        <v>6990284</v>
+        <v>6990254</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1965,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122890348</v>
+        <v>122890344</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -1997,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544083</v>
+        <v>544127</v>
       </c>
       <c r="R14" t="n">
-        <v>6990302</v>
+        <v>6990227</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,10 +2072,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122890363</v>
+        <v>122890349</v>
       </c>
       <c r="B15" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,21 +2088,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2104,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544363</v>
+        <v>544303</v>
       </c>
       <c r="R15" t="n">
-        <v>6990198</v>
+        <v>6990222</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2140,6 +2148,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2166,7 +2179,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122890355</v>
+        <v>122890356</v>
       </c>
       <c r="B16" t="n">
         <v>90970</v>
@@ -2206,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544145</v>
+        <v>544040</v>
       </c>
       <c r="R16" t="n">
-        <v>6990101</v>
+        <v>6990284</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2281,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122890359</v>
+        <v>122890363</v>
       </c>
       <c r="B17" t="n">
         <v>90970</v>
@@ -2308,10 +2321,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544084</v>
+        <v>544363</v>
       </c>
       <c r="R17" t="n">
-        <v>6990233</v>
+        <v>6990198</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2383,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122890350</v>
+        <v>122890339</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2404,16 +2417,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544315</v>
+        <v>544528</v>
       </c>
       <c r="R18" t="n">
-        <v>6990219</v>
+        <v>6990183</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2446,11 +2467,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2477,10 +2493,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122890357</v>
+        <v>122890338</v>
       </c>
       <c r="B19" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2509,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2533,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544392</v>
+        <v>544035</v>
       </c>
       <c r="R19" t="n">
-        <v>6990123</v>
+        <v>6990216</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122890344</v>
+        <v>122890361</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,21 +2611,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2619,10 +2635,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544127</v>
+        <v>544037</v>
       </c>
       <c r="R20" t="n">
-        <v>6990227</v>
+        <v>6990294</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2655,11 +2671,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2686,7 +2697,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122890339</v>
+        <v>122890350</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2720,24 +2731,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544528</v>
+        <v>544315</v>
       </c>
       <c r="R21" t="n">
-        <v>6990183</v>
+        <v>6990219</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,6 +2773,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2796,7 +2804,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122890345</v>
+        <v>122890347</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2830,16 +2838,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544036</v>
+        <v>544037</v>
       </c>
       <c r="R22" t="n">
-        <v>6990229</v>
+        <v>6990296</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,7 +2892,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål 3m upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2903,7 +2919,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122890347</v>
+        <v>122890353</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2937,24 +2953,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544037</v>
+        <v>544396</v>
       </c>
       <c r="R23" t="n">
-        <v>6990296</v>
+        <v>6990125</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2991,7 +2999,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Bohål 3m upp</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3018,7 +3026,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122890342</v>
+        <v>122890346</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3058,10 +3066,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544150</v>
+        <v>544020</v>
       </c>
       <c r="R24" t="n">
-        <v>6990154</v>
+        <v>6990215</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3125,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122890352</v>
+        <v>122890357</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3141,42 +3149,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544346</v>
+        <v>544392</v>
       </c>
       <c r="R25" t="n">
-        <v>6990141</v>
+        <v>6990123</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122890342</v>
+        <v>122890354</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544150</v>
+        <v>544387</v>
       </c>
       <c r="R3" t="n">
-        <v>6990154</v>
+        <v>6990122</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122890358</v>
+        <v>122890339</v>
       </c>
       <c r="B4" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,34 +924,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544106</v>
+        <v>544528</v>
       </c>
       <c r="R4" t="n">
-        <v>6990214</v>
+        <v>6990183</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122890352</v>
+        <v>122890344</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1044,24 +1052,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544346</v>
+        <v>544127</v>
       </c>
       <c r="R5" t="n">
-        <v>6990141</v>
+        <v>6990227</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,6 +1094,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,7 +1125,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122890359</v>
+        <v>122890356</v>
       </c>
       <c r="B6" t="n">
         <v>90970</v>
@@ -1160,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544084</v>
+        <v>544040</v>
       </c>
       <c r="R6" t="n">
-        <v>6990233</v>
+        <v>6990284</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1227,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122890351</v>
+        <v>122890342</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1256,20 +1261,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544331</v>
+        <v>544150</v>
       </c>
       <c r="R7" t="n">
-        <v>6990216</v>
+        <v>6990154</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1307,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,7 +1334,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122890345</v>
+        <v>122890348</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1373,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544036</v>
+        <v>544083</v>
       </c>
       <c r="R8" t="n">
-        <v>6990229</v>
+        <v>6990302</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1414,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122890343</v>
+        <v>122890363</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,21 +1457,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544140</v>
+        <v>544363</v>
       </c>
       <c r="R9" t="n">
-        <v>6990207</v>
+        <v>6990198</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,11 +1517,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1649,7 +1645,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122890348</v>
+        <v>122890343</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1689,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544083</v>
+        <v>544140</v>
       </c>
       <c r="R11" t="n">
-        <v>6990302</v>
+        <v>6990207</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122890354</v>
+        <v>122890361</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,21 +1768,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1796,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544387</v>
+        <v>544037</v>
       </c>
       <c r="R12" t="n">
-        <v>6990122</v>
+        <v>6990294</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,11 +1828,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122890360</v>
+        <v>122890346</v>
       </c>
       <c r="B13" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1903,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544063</v>
+        <v>544020</v>
       </c>
       <c r="R13" t="n">
-        <v>6990254</v>
+        <v>6990215</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,6 +1930,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,7 +1961,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122890344</v>
+        <v>122890347</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -1999,16 +1995,24 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544127</v>
+        <v>544037</v>
       </c>
       <c r="R14" t="n">
-        <v>6990227</v>
+        <v>6990296</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,7 +2049,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Bohål 3m upp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2072,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122890349</v>
+        <v>122890359</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,21 +2092,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2112,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544303</v>
+        <v>544084</v>
       </c>
       <c r="R15" t="n">
-        <v>6990222</v>
+        <v>6990233</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,11 +2152,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,7 +2178,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122890356</v>
+        <v>122890358</v>
       </c>
       <c r="B16" t="n">
         <v>90970</v>
@@ -2219,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544040</v>
+        <v>544106</v>
       </c>
       <c r="R16" t="n">
-        <v>6990284</v>
+        <v>6990214</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2281,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122890363</v>
+        <v>122890345</v>
       </c>
       <c r="B17" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2297,21 +2296,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2321,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544363</v>
+        <v>544036</v>
       </c>
       <c r="R17" t="n">
-        <v>6990198</v>
+        <v>6990229</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,6 +2356,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2383,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122890339</v>
+        <v>122890351</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2419,11 +2423,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544528</v>
+        <v>544331</v>
       </c>
       <c r="R18" t="n">
-        <v>6990183</v>
+        <v>6990216</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,6 +2467,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2595,10 +2600,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122890361</v>
+        <v>122890349</v>
       </c>
       <c r="B20" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2611,21 +2616,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2635,10 +2640,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544037</v>
+        <v>544303</v>
       </c>
       <c r="R20" t="n">
-        <v>6990294</v>
+        <v>6990222</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,6 +2676,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2697,7 +2707,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122890350</v>
+        <v>122890353</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2737,10 +2747,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544315</v>
+        <v>544396</v>
       </c>
       <c r="R21" t="n">
-        <v>6990219</v>
+        <v>6990125</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,7 +2814,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122890347</v>
+        <v>122890350</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2838,24 +2848,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544037</v>
+        <v>544315</v>
       </c>
       <c r="R22" t="n">
-        <v>6990296</v>
+        <v>6990219</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,7 +2894,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Bohål 3m upp</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2919,10 +2921,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122890353</v>
+        <v>122890360</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2935,21 +2937,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2959,10 +2961,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544396</v>
+        <v>544063</v>
       </c>
       <c r="R23" t="n">
-        <v>6990125</v>
+        <v>6990254</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2995,11 +2997,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3026,10 +3023,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122890346</v>
+        <v>122890357</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3042,21 +3039,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3066,10 +3063,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544020</v>
+        <v>544392</v>
       </c>
       <c r="R24" t="n">
-        <v>6990215</v>
+        <v>6990123</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3102,11 +3099,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3133,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122890357</v>
+        <v>122890352</v>
       </c>
       <c r="B25" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3149,34 +3141,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544392</v>
+        <v>544346</v>
       </c>
       <c r="R25" t="n">
-        <v>6990123</v>
+        <v>6990141</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -908,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122890339</v>
+        <v>122890344</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -942,24 +942,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544528</v>
+        <v>544127</v>
       </c>
       <c r="R4" t="n">
-        <v>6990183</v>
+        <v>6990227</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,6 +984,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122890344</v>
+        <v>122890339</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1052,16 +1049,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544127</v>
+        <v>544528</v>
       </c>
       <c r="R5" t="n">
-        <v>6990227</v>
+        <v>6990183</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,11 +1099,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122890354</v>
+        <v>122890355</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>90973</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544387</v>
+        <v>544145</v>
       </c>
       <c r="R3" t="n">
-        <v>6990122</v>
+        <v>6990101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,11 +877,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122890344</v>
+        <v>122890347</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,16 +937,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544127</v>
+        <v>544037</v>
       </c>
       <c r="R4" t="n">
-        <v>6990227</v>
+        <v>6990296</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +991,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Bohål 3m upp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122890339</v>
+        <v>122890338</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,42 +1034,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544528</v>
+        <v>544035</v>
       </c>
       <c r="R5" t="n">
-        <v>6990183</v>
+        <v>6990216</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122890356</v>
+        <v>122890343</v>
       </c>
       <c r="B6" t="n">
-        <v>90970</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544040</v>
+        <v>544140</v>
       </c>
       <c r="R6" t="n">
-        <v>6990284</v>
+        <v>6990207</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,6 +1196,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122890342</v>
+        <v>122890346</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544150</v>
+        <v>544020</v>
       </c>
       <c r="R7" t="n">
-        <v>6990154</v>
+        <v>6990215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
         <v>122890348</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1441,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122890363</v>
+        <v>122890344</v>
       </c>
       <c r="B9" t="n">
-        <v>90970</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,21 +1457,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544363</v>
+        <v>544127</v>
       </c>
       <c r="R9" t="n">
-        <v>6990198</v>
+        <v>6990227</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,6 +1517,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122890355</v>
+        <v>122890356</v>
       </c>
       <c r="B10" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544145</v>
+        <v>544040</v>
       </c>
       <c r="R10" t="n">
-        <v>6990101</v>
+        <v>6990284</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122890343</v>
+        <v>122890351</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,16 +1684,20 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544140</v>
+        <v>544331</v>
       </c>
       <c r="R11" t="n">
-        <v>6990207</v>
+        <v>6990216</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122890361</v>
+        <v>122890342</v>
       </c>
       <c r="B12" t="n">
-        <v>90970</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,21 +1777,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1792,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544037</v>
+        <v>544150</v>
       </c>
       <c r="R12" t="n">
-        <v>6990294</v>
+        <v>6990154</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1828,6 +1837,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1854,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122890346</v>
+        <v>122890353</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544020</v>
+        <v>544396</v>
       </c>
       <c r="R13" t="n">
-        <v>6990215</v>
+        <v>6990125</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122890347</v>
+        <v>122890358</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>90973</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1977,42 +1991,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544037</v>
+        <v>544106</v>
       </c>
       <c r="R14" t="n">
-        <v>6990296</v>
+        <v>6990214</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,11 +2051,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bohål 3m upp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122890359</v>
+        <v>122890345</v>
       </c>
       <c r="B15" t="n">
-        <v>90970</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2092,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544084</v>
+        <v>544036</v>
       </c>
       <c r="R15" t="n">
-        <v>6990233</v>
+        <v>6990229</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,6 +2153,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122890358</v>
+        <v>122890352</v>
       </c>
       <c r="B16" t="n">
-        <v>90970</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2194,34 +2200,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544106</v>
+        <v>544346</v>
       </c>
       <c r="R16" t="n">
-        <v>6990214</v>
+        <v>6990141</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122890345</v>
+        <v>122890359</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>90973</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2296,21 +2310,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544036</v>
+        <v>544084</v>
       </c>
       <c r="R17" t="n">
-        <v>6990229</v>
+        <v>6990233</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,11 +2370,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122890351</v>
+        <v>122890354</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2421,20 +2430,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544331</v>
+        <v>544387</v>
       </c>
       <c r="R18" t="n">
-        <v>6990216</v>
+        <v>6990122</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,7 +2476,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2498,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122890338</v>
+        <v>122890361</v>
       </c>
       <c r="B19" t="n">
-        <v>90952</v>
+        <v>90973</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,21 +2519,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2538,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544035</v>
+        <v>544037</v>
       </c>
       <c r="R19" t="n">
-        <v>6990216</v>
+        <v>6990294</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,7 +2608,7 @@
         <v>122890349</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122890353</v>
+        <v>122890339</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,16 +2746,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544396</v>
+        <v>544528</v>
       </c>
       <c r="R21" t="n">
-        <v>6990125</v>
+        <v>6990183</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,11 +2796,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2814,10 +2822,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122890350</v>
+        <v>122890360</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>90973</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2830,21 +2838,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2854,10 +2862,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544315</v>
+        <v>544063</v>
       </c>
       <c r="R22" t="n">
-        <v>6990219</v>
+        <v>6990254</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,11 +2898,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2921,10 +2924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122890360</v>
+        <v>122890357</v>
       </c>
       <c r="B23" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2961,10 +2964,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544063</v>
+        <v>544392</v>
       </c>
       <c r="R23" t="n">
-        <v>6990254</v>
+        <v>6990123</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3023,10 +3026,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122890357</v>
+        <v>122890363</v>
       </c>
       <c r="B24" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3063,10 +3066,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544392</v>
+        <v>544363</v>
       </c>
       <c r="R24" t="n">
-        <v>6990123</v>
+        <v>6990198</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3125,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122890352</v>
+        <v>122890350</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3159,24 +3162,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544346</v>
+        <v>544315</v>
       </c>
       <c r="R25" t="n">
-        <v>6990141</v>
+        <v>6990219</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3209,6 +3204,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122890355</v>
+        <v>122890358</v>
       </c>
       <c r="B3" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544145</v>
+        <v>544106</v>
       </c>
       <c r="R3" t="n">
-        <v>6990101</v>
+        <v>6990214</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122890347</v>
+        <v>122890349</v>
       </c>
       <c r="B4" t="n">
         <v>57481</v>
@@ -937,24 +937,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544037</v>
+        <v>544303</v>
       </c>
       <c r="R4" t="n">
-        <v>6990296</v>
+        <v>6990222</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +983,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bohål 3m upp</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122890338</v>
+        <v>122890342</v>
       </c>
       <c r="B5" t="n">
-        <v>90955</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,21 +1026,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544035</v>
+        <v>544150</v>
       </c>
       <c r="R5" t="n">
-        <v>6990216</v>
+        <v>6990154</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,6 +1086,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122890343</v>
+        <v>122890348</v>
       </c>
       <c r="B6" t="n">
         <v>57481</v>
@@ -1160,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544140</v>
+        <v>544083</v>
       </c>
       <c r="R6" t="n">
-        <v>6990207</v>
+        <v>6990302</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122890346</v>
+        <v>122890351</v>
       </c>
       <c r="B7" t="n">
         <v>57481</v>
@@ -1261,16 +1258,20 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544020</v>
+        <v>544331</v>
       </c>
       <c r="R7" t="n">
-        <v>6990215</v>
+        <v>6990216</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1308,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122890348</v>
+        <v>122890361</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>90975</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544083</v>
+        <v>544037</v>
       </c>
       <c r="R8" t="n">
-        <v>6990302</v>
+        <v>6990294</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,11 +1411,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122890356</v>
+        <v>122890363</v>
       </c>
       <c r="B10" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544040</v>
+        <v>544363</v>
       </c>
       <c r="R10" t="n">
-        <v>6990284</v>
+        <v>6990198</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1646,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122890351</v>
+        <v>122890353</v>
       </c>
       <c r="B11" t="n">
         <v>57481</v>
@@ -1684,20 +1680,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544331</v>
+        <v>544396</v>
       </c>
       <c r="R11" t="n">
-        <v>6990216</v>
+        <v>6990125</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1726,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122890342</v>
+        <v>122890355</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>90975</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,21 +1769,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1801,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544150</v>
+        <v>544145</v>
       </c>
       <c r="R12" t="n">
-        <v>6990154</v>
+        <v>6990101</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,11 +1829,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,7 +1855,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122890353</v>
+        <v>122890350</v>
       </c>
       <c r="B13" t="n">
         <v>57481</v>
@@ -1908,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544396</v>
+        <v>544315</v>
       </c>
       <c r="R13" t="n">
-        <v>6990125</v>
+        <v>6990219</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122890358</v>
+        <v>122890338</v>
       </c>
       <c r="B14" t="n">
-        <v>90973</v>
+        <v>90957</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,21 +1978,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2015,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544106</v>
+        <v>544035</v>
       </c>
       <c r="R14" t="n">
-        <v>6990214</v>
+        <v>6990216</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,7 +2064,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122890345</v>
+        <v>122890352</v>
       </c>
       <c r="B15" t="n">
         <v>57481</v>
@@ -2111,16 +2098,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544036</v>
+        <v>544346</v>
       </c>
       <c r="R15" t="n">
-        <v>6990229</v>
+        <v>6990141</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,11 +2148,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122890352</v>
+        <v>122890359</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>90975</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,42 +2190,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544346</v>
+        <v>544084</v>
       </c>
       <c r="R16" t="n">
-        <v>6990141</v>
+        <v>6990233</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,10 +2276,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122890359</v>
+        <v>122890354</v>
       </c>
       <c r="B17" t="n">
-        <v>90973</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,21 +2292,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2334,10 +2316,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544084</v>
+        <v>544387</v>
       </c>
       <c r="R17" t="n">
-        <v>6990233</v>
+        <v>6990122</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,6 +2352,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,10 +2383,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122890354</v>
+        <v>122890357</v>
       </c>
       <c r="B18" t="n">
-        <v>57481</v>
+        <v>90975</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,21 +2399,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2423,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544387</v>
+        <v>544392</v>
       </c>
       <c r="R18" t="n">
-        <v>6990122</v>
+        <v>6990123</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,11 +2459,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,10 +2485,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122890361</v>
+        <v>122890345</v>
       </c>
       <c r="B19" t="n">
-        <v>90973</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2519,21 +2501,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2543,10 +2525,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544037</v>
+        <v>544036</v>
       </c>
       <c r="R19" t="n">
-        <v>6990294</v>
+        <v>6990229</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,6 +2561,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,10 +2592,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122890349</v>
+        <v>122890360</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>90975</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,21 +2608,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544303</v>
+        <v>544063</v>
       </c>
       <c r="R20" t="n">
-        <v>6990222</v>
+        <v>6990254</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,11 +2668,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,7 +2694,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122890339</v>
+        <v>122890346</v>
       </c>
       <c r="B21" t="n">
         <v>57481</v>
@@ -2746,24 +2728,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544528</v>
+        <v>544020</v>
       </c>
       <c r="R21" t="n">
-        <v>6990183</v>
+        <v>6990215</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2796,6 +2770,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2822,10 +2801,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122890360</v>
+        <v>122890347</v>
       </c>
       <c r="B22" t="n">
-        <v>90973</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2838,34 +2817,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544063</v>
+        <v>544037</v>
       </c>
       <c r="R22" t="n">
-        <v>6990254</v>
+        <v>6990296</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2898,6 +2885,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bohål 3m upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2924,10 +2916,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122890357</v>
+        <v>122890339</v>
       </c>
       <c r="B23" t="n">
-        <v>90973</v>
+        <v>57481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2940,34 +2932,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544392</v>
+        <v>544528</v>
       </c>
       <c r="R23" t="n">
-        <v>6990123</v>
+        <v>6990183</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122890363</v>
+        <v>122890343</v>
       </c>
       <c r="B24" t="n">
-        <v>90973</v>
+        <v>57481</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544363</v>
+        <v>544140</v>
       </c>
       <c r="R24" t="n">
-        <v>6990198</v>
+        <v>6990207</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3102,6 +3102,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122890350</v>
+        <v>122890356</v>
       </c>
       <c r="B25" t="n">
-        <v>57481</v>
+        <v>90975</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3144,21 +3149,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3168,10 +3173,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544315</v>
+        <v>544040</v>
       </c>
       <c r="R25" t="n">
-        <v>6990219</v>
+        <v>6990284</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,11 +3209,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122890355</v>
+        <v>122890350</v>
       </c>
       <c r="B12" t="n">
-        <v>90975</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544145</v>
+        <v>544315</v>
       </c>
       <c r="R12" t="n">
-        <v>6990101</v>
+        <v>6990219</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,6 +1829,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122890350</v>
+        <v>122890355</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>90975</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1871,21 +1876,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544315</v>
+        <v>544145</v>
       </c>
       <c r="R13" t="n">
-        <v>6990219</v>
+        <v>6990101</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,11 +1936,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 3665-2025 artfynd.xlsx
+++ b/artfynd/A 3665-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122890358</v>
+        <v>122890353</v>
       </c>
       <c r="B3" t="n">
-        <v>90975</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544106</v>
+        <v>544396</v>
       </c>
       <c r="R3" t="n">
-        <v>6990214</v>
+        <v>6990125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,6 +877,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122890349</v>
+        <v>122890348</v>
       </c>
       <c r="B4" t="n">
         <v>57481</v>
@@ -943,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544303</v>
+        <v>544083</v>
       </c>
       <c r="R4" t="n">
-        <v>6990222</v>
+        <v>6990302</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122890342</v>
+        <v>122890361</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>90981</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544150</v>
+        <v>544037</v>
       </c>
       <c r="R5" t="n">
-        <v>6990154</v>
+        <v>6990294</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,11 +1091,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122890348</v>
+        <v>122890359</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>90981</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544083</v>
+        <v>544084</v>
       </c>
       <c r="R6" t="n">
-        <v>6990302</v>
+        <v>6990233</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,11 +1193,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122890351</v>
+        <v>122890344</v>
       </c>
       <c r="B7" t="n">
         <v>57481</v>
@@ -1258,20 +1253,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544331</v>
+        <v>544127</v>
       </c>
       <c r="R7" t="n">
-        <v>6990216</v>
+        <v>6990227</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122890361</v>
+        <v>122890350</v>
       </c>
       <c r="B8" t="n">
-        <v>90975</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,21 +1342,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544037</v>
+        <v>544315</v>
       </c>
       <c r="R8" t="n">
-        <v>6990294</v>
+        <v>6990219</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,6 +1402,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1433,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122890344</v>
+        <v>122890347</v>
       </c>
       <c r="B9" t="n">
         <v>57481</v>
@@ -1471,16 +1467,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544127</v>
+        <v>544037</v>
       </c>
       <c r="R9" t="n">
-        <v>6990227</v>
+        <v>6990296</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1521,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Bohål 3m upp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122890363</v>
+        <v>122890357</v>
       </c>
       <c r="B10" t="n">
-        <v>90975</v>
+        <v>90981</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544363</v>
+        <v>544392</v>
       </c>
       <c r="R10" t="n">
-        <v>6990198</v>
+        <v>6990123</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1650,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122890353</v>
+        <v>122890352</v>
       </c>
       <c r="B11" t="n">
         <v>57481</v>
@@ -1680,16 +1684,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544396</v>
+        <v>544346</v>
       </c>
       <c r="R11" t="n">
-        <v>6990125</v>
+        <v>6990141</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,11 +1734,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122890350</v>
+        <v>122890363</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>90981</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1793,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544315</v>
+        <v>544363</v>
       </c>
       <c r="R12" t="n">
-        <v>6990219</v>
+        <v>6990198</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,11 +1836,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122890355</v>
+        <v>122890360</v>
       </c>
       <c r="B13" t="n">
-        <v>90975</v>
+        <v>90981</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1900,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544145</v>
+        <v>544063</v>
       </c>
       <c r="R13" t="n">
-        <v>6990101</v>
+        <v>6990254</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122890338</v>
+        <v>122890343</v>
       </c>
       <c r="B14" t="n">
-        <v>90957</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544035</v>
+        <v>544140</v>
       </c>
       <c r="R14" t="n">
-        <v>6990216</v>
+        <v>6990207</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,6 +2040,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,7 +2071,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122890352</v>
+        <v>122890349</v>
       </c>
       <c r="B15" t="n">
         <v>57481</v>
@@ -2098,24 +2105,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544346</v>
+        <v>544303</v>
       </c>
       <c r="R15" t="n">
-        <v>6990141</v>
+        <v>6990222</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,6 +2147,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2174,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122890359</v>
+        <v>122890356</v>
       </c>
       <c r="B16" t="n">
-        <v>90975</v>
+        <v>90981</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544084</v>
+        <v>544040</v>
       </c>
       <c r="R16" t="n">
-        <v>6990233</v>
+        <v>6990284</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2383,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122890357</v>
+        <v>122890342</v>
       </c>
       <c r="B18" t="n">
-        <v>90975</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2399,21 +2403,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2423,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544392</v>
+        <v>544150</v>
       </c>
       <c r="R18" t="n">
-        <v>6990123</v>
+        <v>6990154</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2459,6 +2463,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2485,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122890345</v>
+        <v>122890338</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
+        <v>90963</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2501,21 +2510,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2525,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544036</v>
+        <v>544035</v>
       </c>
       <c r="R19" t="n">
-        <v>6990229</v>
+        <v>6990216</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,11 +2570,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2592,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122890360</v>
+        <v>122890339</v>
       </c>
       <c r="B20" t="n">
-        <v>90975</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2608,34 +2612,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544063</v>
+        <v>544528</v>
       </c>
       <c r="R20" t="n">
-        <v>6990254</v>
+        <v>6990183</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,7 +2706,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122890346</v>
+        <v>122890345</v>
       </c>
       <c r="B21" t="n">
         <v>57481</v>
@@ -2734,10 +2746,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544020</v>
+        <v>544036</v>
       </c>
       <c r="R21" t="n">
-        <v>6990215</v>
+        <v>6990229</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2801,7 +2813,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122890347</v>
+        <v>122890346</v>
       </c>
       <c r="B22" t="n">
         <v>57481</v>
@@ -2835,24 +2847,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flärkån, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544037</v>
+        <v>544020</v>
       </c>
       <c r="R22" t="n">
-        <v>6990296</v>
+        <v>6990215</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2889,7 +2893,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Bohål 3m upp</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2916,7 +2920,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122890339</v>
+        <v>122890351</v>
       </c>
       <c r="B23" t="n">
         <v>57481</v>
@@ -2952,11 +2956,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544528</v>
+        <v>544331</v>
       </c>
       <c r="R23" t="n">
-        <v>6990183</v>
+        <v>6990216</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3000,6 +3000,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3026,10 +3031,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122890343</v>
+        <v>122890355</v>
       </c>
       <c r="B24" t="n">
-        <v>57481</v>
+        <v>90981</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3042,21 +3047,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3066,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544140</v>
+        <v>544145</v>
       </c>
       <c r="R24" t="n">
-        <v>6990207</v>
+        <v>6990101</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3102,11 +3107,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3133,10 +3133,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122890356</v>
+        <v>122890358</v>
       </c>
       <c r="B25" t="n">
-        <v>90975</v>
+        <v>90981</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544040</v>
+        <v>544106</v>
       </c>
       <c r="R25" t="n">
-        <v>6990284</v>
+        <v>6990214</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
